--- a/edp/edp_schema_template_v0.1.xlsx
+++ b/edp/edp_schema_template_v0.1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zef22hak/development/COPO_refactoring/COPO-production/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/edp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24EEECBE-4C71-2742-8E08-8D4A3D161A5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B0816E-D127-4E46-B202-4BA72CDC5DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18060" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
   </bookViews>
   <sheets>
-    <sheet name="How to complete the Manifest" sheetId="3" r:id="rId1"/>
+    <sheet name="How to complete the manifest" sheetId="3" r:id="rId1"/>
     <sheet name="sample" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -682,130 +682,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -833,6 +770,69 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1205,13 +1205,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1247,11 +1247,11 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="71"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1269,12 +1269,12 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="55"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1285,20 +1285,20 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="76" t="s">
+      <c r="O4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="71"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="51"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="77"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="57"/>
       <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1311,28 +1311,28 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="78" t="s">
+      <c r="O5" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="80"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="60"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="36"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="70"/>
+      <c r="F6" s="71"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="71"/>
+      <c r="I6" s="71"/>
+      <c r="J6" s="71"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="72"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
@@ -1341,18 +1341,18 @@
       <c r="R6" s="1"/>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="40"/>
+      <c r="A7" s="68"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="45"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1361,19 +1361,19 @@
       <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="45"/>
       <c r="L8" s="8"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1383,20 +1383,20 @@
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="52"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="78"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1405,18 +1405,18 @@
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="53"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="79"/>
       <c r="M10" s="9"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1425,103 +1425,103 @@
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="54"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="80"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="55" t="s">
+      <c r="O11" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="45"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="27"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="58"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
       <c r="L12" s="10"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="48"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="30"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="61"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
       <c r="L13" s="11"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="51"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="33"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="61"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="11"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="65" t="s">
+      <c r="O14" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="40"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="45"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="61"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="39"/>
       <c r="L15" s="11"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -1531,17 +1531,17 @@
       <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="61"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="11"/>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
@@ -1551,17 +1551,17 @@
       <c r="R16" s="1"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="61"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="11"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -1571,17 +1571,17 @@
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="61"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="11"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -1591,17 +1591,17 @@
       <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="61"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="11"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -1611,17 +1611,17 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="61"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="11"/>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -1631,17 +1631,17 @@
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="61"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="11"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -1651,17 +1651,17 @@
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="11"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -1671,17 +1671,17 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="64"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="42"/>
       <c r="L23" s="11"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -1731,11 +1731,11 @@
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
+      <c r="B26" s="62"/>
+      <c r="C26" s="63"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1753,13 +1753,13 @@
       <c r="R26" s="13"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1776,6 +1776,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="E6:L7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K11"/>
+    <mergeCell ref="L9:L11"/>
     <mergeCell ref="O11:R13"/>
     <mergeCell ref="A12:K23"/>
     <mergeCell ref="O14:R14"/>
@@ -1787,13 +1794,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="E6:L7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K11"/>
-    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please select" sqref="L8" xr:uid="{5295E0F2-B1D8-1D4A-9C6B-C01C8ABCA05C}">

--- a/edp/edp_schema_template_v0.1.xlsx
+++ b/edp/edp_schema_template_v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/edp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B0816E-D127-4E46-B202-4BA72CDC5DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1949B029-BEAC-F54C-802B-550A6BC9C36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18060" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
   </bookViews>
@@ -260,10 +260,10 @@
     <t>For the use of Earlham Institute only - DO NOT EDIT</t>
   </si>
   <si>
-    <t>Instructions for completing the Manifest.</t>
+    <t>Do not edit fields highlighted in grey, these are for Earlham Institute use only</t>
   </si>
   <si>
-    <t>Do not edit fields highlighted in grey, these are for Earlham Institute use only</t>
+    <t>Instructions for completing the manifest.</t>
   </si>
 </sst>
 </file>
@@ -682,67 +682,130 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -770,69 +833,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1177,7 +1177,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1" s="20"/>
     </row>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="3" spans="1:2" ht="29" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="24"/>
     </row>
@@ -1205,13 +1205,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="48"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="68"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1247,11 +1247,11 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="71"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1269,12 +1269,12 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="72" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="55"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="75"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1285,20 +1285,20 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="56" t="s">
+      <c r="O4" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="53"/>
-      <c r="Q4" s="51"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="71"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="54"/>
-      <c r="D5" s="57"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="77"/>
       <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1311,28 +1311,28 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="58" t="s">
+      <c r="O5" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="60"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="80"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="67"/>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="72"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="36"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
@@ -1341,18 +1341,18 @@
       <c r="R6" s="1"/>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="68"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="45"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="39"/>
+      <c r="L7" s="40"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1361,19 +1361,19 @@
       <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="45"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="40"/>
       <c r="L8" s="8"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1383,20 +1383,20 @@
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="77" t="s">
+      <c r="A9" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="78"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="52"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1405,18 +1405,18 @@
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="79"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="9"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1425,103 +1425,103 @@
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="80"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="54"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="25" t="s">
+      <c r="O11" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="27"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+      <c r="R11" s="45"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="36"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="K12" s="58"/>
       <c r="L12" s="10"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="28"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="30"/>
+      <c r="O12" s="46"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="48"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="39"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="60"/>
+      <c r="E13" s="60"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="61"/>
       <c r="L13" s="11"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="33"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="51"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="39"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
       <c r="L14" s="11"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="43" t="s">
+      <c r="O14" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="44"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="45"/>
+      <c r="P14" s="39"/>
+      <c r="Q14" s="39"/>
+      <c r="R14" s="40"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="39"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="60"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
       <c r="L15" s="11"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -1531,17 +1531,17 @@
       <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="39"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="61"/>
       <c r="L16" s="11"/>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
@@ -1551,17 +1551,17 @@
       <c r="R16" s="1"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="39"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
       <c r="L17" s="11"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -1571,17 +1571,17 @@
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="37"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="39"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="60"/>
+      <c r="G18" s="60"/>
+      <c r="H18" s="60"/>
+      <c r="I18" s="60"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="61"/>
       <c r="L18" s="11"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -1591,17 +1591,17 @@
       <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="61"/>
       <c r="L19" s="11"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -1611,17 +1611,17 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="37"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="38"/>
-      <c r="D20" s="38"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="61"/>
       <c r="L20" s="11"/>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -1631,17 +1631,17 @@
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="37"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="60"/>
+      <c r="K21" s="61"/>
       <c r="L21" s="11"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -1651,17 +1651,17 @@
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="37"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="38"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
+      <c r="A22" s="59"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+      <c r="J22" s="60"/>
+      <c r="K22" s="61"/>
       <c r="L22" s="11"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -1671,17 +1671,17 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="41"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="41"/>
-      <c r="K23" s="42"/>
+      <c r="A23" s="62"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
+      <c r="F23" s="63"/>
+      <c r="G23" s="63"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="63"/>
+      <c r="J23" s="63"/>
+      <c r="K23" s="64"/>
       <c r="L23" s="11"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -1731,11 +1731,11 @@
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="61" t="s">
+      <c r="A26" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B26" s="62"/>
-      <c r="C26" s="63"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="27"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1753,13 +1753,13 @@
       <c r="R26" s="13"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="64" t="s">
+      <c r="A27" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="65"/>
-      <c r="C27" s="65"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="65"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1776,13 +1776,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="E6:L7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K11"/>
-    <mergeCell ref="L9:L11"/>
     <mergeCell ref="O11:R13"/>
     <mergeCell ref="A12:K23"/>
     <mergeCell ref="O14:R14"/>
@@ -1794,6 +1787,13 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="E6:L7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K11"/>
+    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please select" sqref="L8" xr:uid="{5295E0F2-B1D8-1D4A-9C6B-C01C8ABCA05C}">

--- a/edp/edp_schema_template_v0.1.xlsx
+++ b/edp/edp_schema_template_v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/edp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1949B029-BEAC-F54C-802B-550A6BC9C36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24CC8F3-532C-DC48-9517-9180F36FD079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18060" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
+    <workbookView xWindow="4980" yWindow="4240" windowWidth="30240" windowHeight="12520" activeTab="1" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
   </bookViews>
   <sheets>
     <sheet name="How to complete the manifest" sheetId="3" r:id="rId1"/>
@@ -139,10 +139,25 @@
     <t>Fields in blue are optional</t>
   </si>
   <si>
-    <t>Email address(es) of person(s) who final data should be sent to</t>
+    <t>Do you require samples to be returned to you (at your cost) on completion of the project?</t>
   </si>
   <si>
-    <t>Do you require samples to be returned to you (at your cost) on completion of the project?</t>
+    <t>SAMPLE DETAILS</t>
+  </si>
+  <si>
+    <t>For the use of Earlham Institute only - DO NOT EDIT</t>
+  </si>
+  <si>
+    <t>Do not edit the fields highlighted in grey because they are reserved for use by the Earlham Institute.</t>
+  </si>
+  <si>
+    <t>Instructions for completing the manifest</t>
+  </si>
+  <si>
+    <t>projects@earlham.ac.uk</t>
+  </si>
+  <si>
+    <t>Please complete this manifest and return it to the Project Management (PM) team by email before submitting your samples.</t>
   </si>
   <si>
     <r>
@@ -163,11 +178,11 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-By submitting this manifest to EI you are confirming that, if relevant, you have informed us of any potential health and safety risks associated with the samples. Please select </t>
+By submitting this manifest to the Earlham Insititue (EI), you are confirming that if relevant, you have informed us of any potential health and safety risks associated with the samples. Please select </t>
     </r>
     <r>
       <rPr>
-        <u/>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -184,9 +199,6 @@
       </rPr>
       <t xml:space="preserve"> (in the box to the right) to confirm you have read and understood this message.</t>
     </r>
-  </si>
-  <si>
-    <t>Please complete this manifest and return it to our Project Management team by email before submitting your samples.</t>
   </si>
   <si>
     <r>
@@ -207,7 +219,7 @@
     </r>
     <r>
       <rPr>
-        <u/>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
@@ -222,17 +234,17 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> column, in the </t>
+      <t xml:space="preserve"> column in the </t>
     </r>
     <r>
       <rPr>
-        <u/>
+        <b/>
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Sample Details</t>
+      <t>SAMPLE DETAILS</t>
     </r>
     <r>
       <rPr>
@@ -241,36 +253,56 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> table of this manifest, for all samples submitted to EI.
+      <t xml:space="preserve"> section of this manifest for all samples submitted to EI.
+If you are unsure whether any of the regulations apply, please contact </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>projects@earlham.ac.uk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.
  ♦ CITES - https://cites.org/eng
  ♦ Plant Health Regulations - https://www.gov.uk/guidance/plant-health-controls
  ♦ Human Tissue Act - https://www.hta.gov.uk/guidance-professionals/hta-legislation
  ♦ Nagoya Protocol - https://www.cbd.int/abs/about/ 
  ♦ UK GDPR &amp; The Data Protection Act 2018 - https://www.gov.uk/data-protection EU-GDPR https://gdpr.eu/tag/gdpr/ 
-     International data protection laws/regulations - https://www.dlapiperdataprotection.com/</t>
+    International data protection laws/regulations - https://www.dlapiperdataprotection.com/</t>
     </r>
   </si>
   <si>
-    <t>mailto:projects@earlham.ac.uk</t>
-  </si>
-  <si>
-    <t>SAMPLE DETAILS</t>
-  </si>
-  <si>
-    <t>For the use of Earlham Institute only - DO NOT EDIT</t>
-  </si>
-  <si>
-    <t>Do not edit fields highlighted in grey, these are for Earlham Institute use only</t>
-  </si>
-  <si>
-    <t>Instructions for completing the manifest.</t>
+    <r>
+      <t xml:space="preserve">Email address(es) of person(s) whom the sequencing data should be sent to
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Separate multiple addresses with a semicolon and a space</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -340,13 +372,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF0A0101"/>
       <name val="Arial"/>
@@ -355,12 +380,6 @@
     <font>
       <sz val="12"/>
       <color rgb="FFCC0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -384,7 +403,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -417,12 +436,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -439,6 +452,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E0B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="16">
     <border>
@@ -622,7 +647,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -635,16 +660,16 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -658,16 +683,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -689,10 +714,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -707,7 +732,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -765,14 +790,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -804,9 +829,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -826,13 +848,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -840,6 +873,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC6E0B4"/>
+      <color rgb="FFBDD7EF"/>
+      <color rgb="FFDBF2D1"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1177,7 +1217,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" ht="21" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B1" s="20"/>
     </row>
@@ -1185,9 +1225,9 @@
       <c r="A2" s="21"/>
       <c r="B2" s="22"/>
     </row>
-    <row r="3" spans="1:2" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B3" s="24"/>
     </row>
@@ -1205,13 +1245,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="68"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="67"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1247,11 +1287,11 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="71"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1269,12 +1309,12 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="75"/>
+      <c r="B4" s="72"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1285,20 +1325,20 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="76" t="s">
+      <c r="O4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="71"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="81"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="77"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="75"/>
       <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1311,16 +1351,16 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="78" t="s">
+      <c r="O5" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="80"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="78"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="30" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
@@ -1340,7 +1380,7 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32"/>
       <c r="B7" s="33"/>
       <c r="C7" s="33"/>
@@ -1362,7 +1402,7 @@
     </row>
     <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="42"/>
@@ -1384,7 +1424,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="43" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B9" s="44"/>
       <c r="C9" s="44"/>
@@ -1440,15 +1480,15 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="55" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P11" s="44"/>
       <c r="Q11" s="44"/>
       <c r="R11" s="45"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="56" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
@@ -1503,12 +1543,12 @@
       <c r="L14" s="11"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="65" t="s">
+      <c r="O14" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="39"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="40"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="84"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="59"/>
@@ -1670,7 +1710,7 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="1:18" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="62"/>
       <c r="B23" s="63"/>
       <c r="C23" s="63"/>
@@ -1732,7 +1772,7 @@
     </row>
     <row r="26" spans="1:18" ht="20" x14ac:dyDescent="0.2">
       <c r="A26" s="25" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B26" s="26"/>
       <c r="C26" s="27"/>
@@ -1754,7 +1794,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B27" s="29"/>
       <c r="C27" s="29"/>
@@ -1795,7 +1835,7 @@
     <mergeCell ref="A9:K11"/>
     <mergeCell ref="L9:L11"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="3">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please select" sqref="L8" xr:uid="{5295E0F2-B1D8-1D4A-9C6B-C01C8ABCA05C}">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
@@ -1808,9 +1848,10 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="O14:Q14" r:id="rId1" display="mailto:projects@earlham.ac.uk" xr:uid="{49881876-F596-AF42-A642-110708396225}"/>
-    <hyperlink ref="O14" r:id="rId2" xr:uid="{7A0622C2-AB1B-5649-A342-F913056CB9F6}"/>
+    <hyperlink ref="O14" r:id="rId2" display="mailto:projects@earlham.ac.uk" xr:uid="{7A0622C2-AB1B-5649-A342-F913056CB9F6}"/>
+    <hyperlink ref="O14:R14" r:id="rId3" display="projects@earlham.ac.uk" xr:uid="{A88255CC-B8C3-A149-AD45-1D5DF6AEA7AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
--- a/edp/edp_schema_template_v0.1.xlsx
+++ b/edp/edp_schema_template_v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/edp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24CC8F3-532C-DC48-9517-9180F36FD079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6911740C-0375-114F-9167-3E806C049113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4240" windowWidth="30240" windowHeight="12520" activeTab="1" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
+    <workbookView xWindow="10220" yWindow="5560" windowWidth="30240" windowHeight="12520" activeTab="1" xr2:uid="{964001A8-9378-804A-8584-54773ECBCFFA}"/>
   </bookViews>
   <sheets>
     <sheet name="How to complete the manifest" sheetId="3" r:id="rId1"/>
@@ -161,47 +161,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Health and Safety</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-By submitting this manifest to the Earlham Insititue (EI), you are confirming that if relevant, you have informed us of any potential health and safety risks associated with the samples. Please select </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>YES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (in the box to the right) to confirm you have read and understood this message.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Legal
 </t>
     </r>
@@ -284,7 +243,48 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Email address(es) of person(s) whom the sequencing data should be sent to
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Health and Safety</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+By submitting this manifest to the Earlham Insititute (EI), you are confirming that if relevant, you have informed us of any potential health and safety risks associated with the samples. Please select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>YES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (in the box to the right) to confirm you have read and understood this message.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Email address(es) of person(s) to whom the final sequencing data should be sent to
 </t>
     </r>
     <r>
@@ -294,7 +294,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>Separate multiple addresses with a semicolon and a space</t>
+      <t>Separate multiple addresses with a semicolon or a space</t>
     </r>
   </si>
 </sst>
@@ -707,128 +707,68 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -848,23 +788,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1241,17 +1241,19 @@
   <dimension ref="A1:R27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="28" width="18.6640625" customWidth="1"/>
+    <col min="1" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="28" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="26" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="67"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1287,11 +1289,11 @@
       <c r="R2" s="1"/>
     </row>
     <row r="3" spans="1:18" ht="21" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="70"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -1309,12 +1311,12 @@
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="74"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="55"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -1325,20 +1327,20 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="79" t="s">
+      <c r="O4" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="80"/>
-      <c r="Q4" s="81"/>
+      <c r="P4" s="57"/>
+      <c r="Q4" s="58"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="75"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="59"/>
       <c r="E5" s="6" t="s">
         <v>5</v>
       </c>
@@ -1351,28 +1353,28 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="76" t="s">
+      <c r="O5" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="78"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="62"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="36"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="72"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="74"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="2"/>
@@ -1380,19 +1382,19 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="23" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="40"/>
+    <row r="7" spans="1:18" ht="34" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="70"/>
+      <c r="B7" s="71"/>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="78"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -1401,19 +1403,19 @@
       <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="G8" s="77"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="77"/>
+      <c r="J8" s="77"/>
+      <c r="K8" s="78"/>
       <c r="L8" s="8"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1423,20 +1425,20 @@
       <c r="R8" s="1"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="43" t="s">
-        <v>14</v>
+      <c r="A9" s="81" t="s">
+        <v>15</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="52"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="82"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -1445,18 +1447,18 @@
       <c r="R9" s="1"/>
     </row>
     <row r="10" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="48"/>
-      <c r="L10" s="53"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="83"/>
       <c r="M10" s="9"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -1465,103 +1467,103 @@
       <c r="R10" s="1"/>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="54"/>
+      <c r="A11" s="31"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="84"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-      <c r="O11" s="55" t="s">
+      <c r="O11" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="45"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="27"/>
     </row>
     <row r="12" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="56" t="s">
-        <v>15</v>
+      <c r="A12" s="34" t="s">
+        <v>14</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="57"/>
-      <c r="K12" s="58"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
       <c r="L12" s="10"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-      <c r="O12" s="46"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="48"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="30"/>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="59"/>
-      <c r="B13" s="60"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="60"/>
-      <c r="E13" s="60"/>
-      <c r="F13" s="60"/>
-      <c r="G13" s="60"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="60"/>
-      <c r="J13" s="60"/>
-      <c r="K13" s="61"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
       <c r="L13" s="11"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
-      <c r="O13" s="49"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="51"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="33"/>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="59"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
-      <c r="F14" s="60"/>
-      <c r="G14" s="60"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="60"/>
-      <c r="J14" s="60"/>
-      <c r="K14" s="61"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
       <c r="L14" s="11"/>
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
-      <c r="O14" s="82" t="s">
+      <c r="O14" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="84"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="45"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="59"/>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="60"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="60"/>
-      <c r="K15" s="61"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="39"/>
       <c r="L15" s="11"/>
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
@@ -1571,17 +1573,17 @@
       <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="61"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="39"/>
       <c r="L16" s="11"/>
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
@@ -1591,17 +1593,17 @@
       <c r="R16" s="1"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="59"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
-      <c r="F17" s="60"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="61"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="39"/>
       <c r="L17" s="11"/>
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
@@ -1611,17 +1613,17 @@
       <c r="R17" s="1"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="59"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="60"/>
-      <c r="E18" s="60"/>
-      <c r="F18" s="60"/>
-      <c r="G18" s="60"/>
-      <c r="H18" s="60"/>
-      <c r="I18" s="60"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="61"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="39"/>
       <c r="L18" s="11"/>
       <c r="M18" s="12"/>
       <c r="N18" s="12"/>
@@ -1631,17 +1633,17 @@
       <c r="R18" s="1"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="59"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="61"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="39"/>
       <c r="L19" s="11"/>
       <c r="M19" s="12"/>
       <c r="N19" s="12"/>
@@ -1651,17 +1653,17 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="59"/>
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="61"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="11"/>
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
@@ -1671,17 +1673,17 @@
       <c r="R20" s="1"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="60"/>
-      <c r="H21" s="60"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="60"/>
-      <c r="K21" s="61"/>
+      <c r="A21" s="37"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="39"/>
       <c r="L21" s="11"/>
       <c r="M21" s="12"/>
       <c r="N21" s="12"/>
@@ -1691,17 +1693,17 @@
       <c r="R21" s="1"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="38"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="38"/>
+      <c r="K22" s="39"/>
       <c r="L22" s="11"/>
       <c r="M22" s="12"/>
       <c r="N22" s="12"/>
@@ -1711,17 +1713,17 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="62"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="64"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="42"/>
       <c r="L23" s="11"/>
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
@@ -1771,11 +1773,11 @@
       <c r="R25" s="1"/>
     </row>
     <row r="26" spans="1:18" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="27"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="65"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
@@ -1793,13 +1795,13 @@
       <c r="R26" s="13"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1816,6 +1818,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A6:D7"/>
+    <mergeCell ref="E6:L7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K11"/>
+    <mergeCell ref="L9:L11"/>
     <mergeCell ref="O11:R13"/>
     <mergeCell ref="A12:K23"/>
     <mergeCell ref="O14:R14"/>
@@ -1827,13 +1836,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A6:D7"/>
-    <mergeCell ref="E6:L7"/>
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K11"/>
-    <mergeCell ref="L9:L11"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Please select" sqref="L8" xr:uid="{5295E0F2-B1D8-1D4A-9C6B-C01C8ABCA05C}">
